--- a/Money supply.xlsx
+++ b/Money supply.xlsx
@@ -1127,7 +1127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P171"/>
+  <dimension ref="A1:P173"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.90625" defaultRowHeight="13"/>
   <cols>
     <col width="5.6328125" customWidth="1" style="10" min="1" max="1"/>
@@ -9128,8 +9128,94 @@
         <v>4940.33997399965</v>
       </c>
     </row>
-    <row r="172" ht="14.5" customHeight="1"/>
-    <row r="173" ht="14.5" customHeight="1"/>
+    <row r="172" ht="14.5" customHeight="1">
+      <c r="B172" t="n">
+        <v>6</v>
+      </c>
+      <c r="D172" t="n">
+        <v>2670359.95724294</v>
+      </c>
+      <c r="E172" t="n">
+        <v>2665315.77217994</v>
+      </c>
+      <c r="F172" t="n">
+        <v>742082.14905194</v>
+      </c>
+      <c r="G172" t="n">
+        <v>170172.25623394</v>
+      </c>
+      <c r="H172" t="n">
+        <v>571909.8928180001</v>
+      </c>
+      <c r="I172" t="n">
+        <v>1923233.623128</v>
+      </c>
+      <c r="J172" t="n">
+        <v>249158.769072</v>
+      </c>
+      <c r="K172" t="n">
+        <v>1072577.458234</v>
+      </c>
+      <c r="L172" t="n">
+        <v>2190.125468</v>
+      </c>
+      <c r="M172" t="n">
+        <v>791.400162</v>
+      </c>
+      <c r="N172" t="n">
+        <v>364161.543134</v>
+      </c>
+      <c r="O172" t="n">
+        <v>234354.327058</v>
+      </c>
+      <c r="P172" t="n">
+        <v>5044.18506299984</v>
+      </c>
+    </row>
+    <row r="173" ht="14.5" customHeight="1">
+      <c r="B173" t="n">
+        <v>7</v>
+      </c>
+      <c r="D173" t="n">
+        <v>2659386.3349648</v>
+      </c>
+      <c r="E173" t="n">
+        <v>2653943.9556038</v>
+      </c>
+      <c r="F173" t="n">
+        <v>736245.1870658</v>
+      </c>
+      <c r="G173" t="n">
+        <v>171156.6009768</v>
+      </c>
+      <c r="H173" t="n">
+        <v>565088.586089</v>
+      </c>
+      <c r="I173" t="n">
+        <v>1917698.768538</v>
+      </c>
+      <c r="J173" t="n">
+        <v>247264.820329</v>
+      </c>
+      <c r="K173" t="n">
+        <v>1081679.296182</v>
+      </c>
+      <c r="L173" t="n">
+        <v>1792.244109</v>
+      </c>
+      <c r="M173" t="n">
+        <v>791.400162</v>
+      </c>
+      <c r="N173" t="n">
+        <v>358117.602631</v>
+      </c>
+      <c r="O173" t="n">
+        <v>228053.405125</v>
+      </c>
+      <c r="P173" t="n">
+        <v>5442.37936100038</v>
+      </c>
+    </row>
     <row r="174" ht="14.5" customHeight="1"/>
     <row r="175" ht="14.5" customHeight="1"/>
     <row r="176" ht="14.5" customHeight="1"/>

--- a/Money supply.xlsx
+++ b/Money supply.xlsx
@@ -1127,7 +1127,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P173"/>
+  <dimension ref="A1:P174"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.90625" defaultRowHeight="13"/>
   <cols>
     <col width="5.6328125" customWidth="1" style="10" min="1" max="1"/>
@@ -9216,7 +9216,50 @@
         <v>5442.37936100038</v>
       </c>
     </row>
-    <row r="174" ht="14.5" customHeight="1"/>
+    <row r="174" ht="14.5" customHeight="1">
+      <c r="B174" t="n">
+        <v>8</v>
+      </c>
+      <c r="D174" t="n">
+        <v>2636548.76686104</v>
+      </c>
+      <c r="E174" t="n">
+        <v>2631087.55189604</v>
+      </c>
+      <c r="F174" t="n">
+        <v>741827.13024404</v>
+      </c>
+      <c r="G174" t="n">
+        <v>172584.60984104</v>
+      </c>
+      <c r="H174" t="n">
+        <v>569242.5204029999</v>
+      </c>
+      <c r="I174" t="n">
+        <v>1889260.421652</v>
+      </c>
+      <c r="J174" t="n">
+        <v>244955.146261</v>
+      </c>
+      <c r="K174" t="n">
+        <v>1087174.941977</v>
+      </c>
+      <c r="L174" t="n">
+        <v>1823.974077</v>
+      </c>
+      <c r="M174" t="n">
+        <v>791.406285</v>
+      </c>
+      <c r="N174" t="n">
+        <v>334890.257288</v>
+      </c>
+      <c r="O174" t="n">
+        <v>219624.695764</v>
+      </c>
+      <c r="P174" t="n">
+        <v>5461.21496500028</v>
+      </c>
+    </row>
     <row r="175" ht="14.5" customHeight="1"/>
     <row r="176" ht="14.5" customHeight="1"/>
     <row r="177" ht="14.5" customHeight="1"/>
